--- a/trading_signals/risk_management/risk_workbook_20260609_031841.xlsx
+++ b/trading_signals/risk_management/risk_workbook_20260609_031841.xlsx
@@ -728,7 +728,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Signal date 2026-06-08  ·  Generated 2026-06-10T09:48:42  ·  Scope: MRPT+MTFS pairs book (model-based, broker-reconciled)</t>
+          <t>Signal date 2026-06-08  ·  Generated 2026-06-24T18:50:42  ·  Scope: MRPT+MTFS pairs book (model-based, broker-reconciled)</t>
         </is>
       </c>
     </row>
@@ -739,7 +739,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>1063725.16</v>
+        <v>1063800.8</v>
       </c>
     </row>
     <row r="5">
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>17.64</v>
+        <v>17.63</v>
       </c>
     </row>
     <row r="11">
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>1.186</v>
+        <v>1.185</v>
       </c>
     </row>
     <row r="12">
@@ -819,7 +819,7 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>0.8152</v>
+        <v>0.8149999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>8.85</v>
+        <v>8.859999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -840,7 +840,7 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>4.26 / 2.13</t>
+          <t>4.25 / 2.13</t>
         </is>
       </c>
     </row>
@@ -862,7 +862,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>STLD (22.31% NAV)</t>
+          <t>STLD (22.3% NAV)</t>
         </is>
       </c>
     </row>
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>17.64</v>
+        <v>17.63</v>
       </c>
     </row>
     <row r="7">
@@ -1243,11 +1243,11 @@
           <t>KLAC/REGN</t>
         </is>
       </c>
-      <c r="C8" s="11" t="n">
-        <v>67</v>
+      <c r="C8" s="4" t="n">
+        <v>670</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>1014028</v>
+        <v>1538684</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>0</v>
@@ -1558,7 +1558,7 @@
         </is>
       </c>
       <c r="B4" s="19" t="n">
-        <v>-41804.4</v>
+        <v>-41807.37</v>
       </c>
       <c r="C4" s="22" t="n">
         <v>-3.93</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="B5" s="18" t="n">
-        <v>-83608.8</v>
+        <v>-83614.74000000001</v>
       </c>
       <c r="C5" s="23" t="n">
         <v>-7.86</v>
@@ -1584,7 +1584,7 @@
         </is>
       </c>
       <c r="B6" s="19" t="n">
-        <v>-41804.4</v>
+        <v>-41807.37</v>
       </c>
       <c r="C6" s="22" t="n">
         <v>-3.93</v>
@@ -1731,7 +1731,7 @@
         </is>
       </c>
       <c r="C6" s="30" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="D6" s="30" t="n">
         <v>3</v>
@@ -1783,7 +1783,7 @@
         </is>
       </c>
       <c r="C8" s="34" t="n">
-        <v>22.31</v>
+        <v>22.3</v>
       </c>
       <c r="D8" s="34" t="n">
         <v>15</v>
@@ -2199,10 +2199,10 @@
         </is>
       </c>
       <c r="E6" s="26" t="n">
-        <v>67</v>
+        <v>670</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>2108.06</v>
+        <v>210.81</v>
       </c>
       <c r="G6" s="13" t="n">
         <v>141240.02</v>
@@ -3304,16 +3304,16 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>14.77</v>
+        <v>15.1</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.34</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>25</v>
       </c>
       <c r="E6" s="22" t="n">
-        <v>-14.7</v>
+        <v>-14.76</v>
       </c>
     </row>
     <row r="7">
@@ -3323,16 +3323,16 @@
         </is>
       </c>
       <c r="B7" s="17" t="n">
-        <v>12.82</v>
+        <v>13.15</v>
       </c>
       <c r="C7" s="17" t="n">
-        <v>19.4</v>
+        <v>23.56</v>
       </c>
       <c r="D7" s="17" t="n">
         <v>25</v>
       </c>
       <c r="E7" s="20" t="n">
-        <v>6.58</v>
+        <v>10.41</v>
       </c>
     </row>
     <row r="8">
@@ -3342,16 +3342,16 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>24.85</v>
+        <v>25.43</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>3.21</v>
+        <v>3.66</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>25</v>
       </c>
       <c r="E8" s="22" t="n">
-        <v>-21.65</v>
+        <v>-21.77</v>
       </c>
     </row>
     <row r="9">
@@ -3361,16 +3361,16 @@
         </is>
       </c>
       <c r="B9" s="17" t="n">
-        <v>47.55</v>
+        <v>46.32</v>
       </c>
       <c r="C9" s="17" t="n">
-        <v>77.31999999999999</v>
+        <v>72.44</v>
       </c>
       <c r="D9" s="17" t="n">
         <v>25</v>
       </c>
       <c r="E9" s="20" t="n">
-        <v>29.77</v>
+        <v>26.12</v>
       </c>
     </row>
     <row r="11">
@@ -3580,7 +3580,7 @@
         </is>
       </c>
       <c r="B5" s="21" t="n">
-        <v>38.97</v>
+        <v>38.94</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>2.6</v>
@@ -3613,7 +3613,7 @@
       </c>
       <c r="J5" s="7" t="inlineStr">
         <is>
-          <t>-0.111 (t=-0.62)</t>
+          <t>-0.11 (t=-0.62)</t>
         </is>
       </c>
       <c r="K5" s="7" t="inlineStr">
@@ -3629,10 +3629,10 @@
         </is>
       </c>
       <c r="B6" s="20" t="n">
-        <v>48.07</v>
+        <v>47.74</v>
       </c>
       <c r="C6" s="17" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="D6" s="17" t="n">
         <v>0.059</v>
@@ -3642,27 +3642,27 @@
       </c>
       <c r="F6" s="17" t="inlineStr">
         <is>
-          <t>0.056 (t=0.39)</t>
+          <t>0.059 (t=0.41)</t>
         </is>
       </c>
       <c r="G6" s="17" t="inlineStr">
         <is>
-          <t>-0.116 (t=-0.52)</t>
+          <t>-0.119 (t=-0.54)</t>
         </is>
       </c>
       <c r="H6" s="17" t="inlineStr">
         <is>
-          <t>-0.06 (t=-0.31)</t>
+          <t>-0.059 (t=-0.3)</t>
         </is>
       </c>
       <c r="I6" s="17" t="inlineStr">
         <is>
-          <t>0.241 (t=1.31)</t>
+          <t>0.244 (t=1.32)</t>
         </is>
       </c>
       <c r="J6" s="17" t="inlineStr">
         <is>
-          <t>-0.207 (t=-0.72)</t>
+          <t>-0.208 (t=-0.72)</t>
         </is>
       </c>
       <c r="K6" s="17" t="inlineStr">
@@ -3678,7 +3678,7 @@
         </is>
       </c>
       <c r="B7" s="21" t="n">
-        <v>28.62</v>
+        <v>29.07</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>1.03</v>
@@ -3691,32 +3691,32 @@
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>-0.069 (t=-0.42)</t>
+          <t>-0.073 (t=-0.44)</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>-0.004 (t=-0.02)</t>
+          <t>0.001 (t=0.0)</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>0.235 (t=1.04)</t>
+          <t>0.234 (t=1.03)</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>-0.103 (t=-0.49)</t>
+          <t>-0.106 (t=-0.5)</t>
         </is>
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
-          <t>0.022 (t=0.07)</t>
+          <t>0.023 (t=0.07)</t>
         </is>
       </c>
       <c r="K7" s="7" t="inlineStr">
         <is>
-          <t>-0.065 (t=-0.55)</t>
+          <t>-0.064 (t=-0.53)</t>
         </is>
       </c>
     </row>
@@ -3805,10 +3805,10 @@
         </is>
       </c>
       <c r="B4" s="7" t="n">
-        <v>0.16</v>
+        <v>0.164</v>
       </c>
       <c r="C4" s="7" t="n">
-        <v>25.081</v>
+        <v>25.131</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>0</v>
@@ -3817,10 +3817,10 @@
         <v>1</v>
       </c>
       <c r="F4" s="7" t="n">
-        <v>2.238</v>
+        <v>2.242</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>2.238</v>
+        <v>2.242</v>
       </c>
       <c r="H4" s="7" t="n">
         <v>0</v>
@@ -3833,10 +3833,10 @@
         </is>
       </c>
       <c r="B5" s="17" t="n">
-        <v>-0.387</v>
+        <v>-0.424</v>
       </c>
       <c r="C5" s="17" t="n">
-        <v>2.314</v>
+        <v>2.446</v>
       </c>
       <c r="D5" s="17" t="n">
         <v>0</v>
@@ -3845,13 +3845,13 @@
         <v>1</v>
       </c>
       <c r="F5" s="17" t="n">
-        <v>1.597</v>
+        <v>1.605</v>
       </c>
       <c r="G5" s="17" t="n">
-        <v>1.659</v>
+        <v>1.675</v>
       </c>
       <c r="H5" s="17" t="n">
-        <v>0.062</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -3861,10 +3861,10 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>1.611</v>
+        <v>1.613</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>29.738</v>
+        <v>29.592</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>0</v>
@@ -3873,10 +3873,10 @@
         <v>1</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>4.815</v>
+        <v>4.82</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>4.815</v>
+        <v>4.82</v>
       </c>
       <c r="H6" s="7" t="n">
         <v>0</v>
@@ -3941,16 +3941,16 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>1.186</v>
+        <v>1.185</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>0.8152</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>8.85</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="F9" s="7" t="n">
         <v>9.470000000000001</v>
@@ -3959,7 +3959,7 @@
         <v>76</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>4.26</v>
+        <v>4.25</v>
       </c>
       <c r="I9" s="7" t="n">
         <v>2.13</v>
@@ -3975,13 +3975,13 @@
         </is>
       </c>
       <c r="B10" s="17" t="n">
-        <v>1.249</v>
+        <v>1.225</v>
       </c>
       <c r="C10" s="17" t="n">
-        <v>0.8263</v>
+        <v>0.8215</v>
       </c>
       <c r="D10" s="17" t="n">
-        <v>455</v>
+        <v>473</v>
       </c>
       <c r="E10" s="17" t="n">
         <v>8.880000000000001</v>
@@ -3993,10 +3993,10 @@
         <v>76.7</v>
       </c>
       <c r="H10" s="17" t="n">
-        <v>5.81</v>
+        <v>5.65</v>
       </c>
       <c r="I10" s="17" t="n">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="J10" s="17" t="n">
         <v>0.245</v>
@@ -4009,13 +4009,13 @@
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>0.873</v>
+        <v>0.88</v>
       </c>
       <c r="C11" s="7" t="n">
-        <v>0.7554</v>
+        <v>0.7573</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>838</v>
+        <v>824</v>
       </c>
       <c r="E11" s="7" t="n">
         <v>15.56</v>
@@ -4027,13 +4027,13 @@
         <v>79.3</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="J11" s="7" t="n">
-        <v>2.357</v>
+        <v>2.352</v>
       </c>
     </row>
   </sheetData>
@@ -4108,7 +4108,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>150095.98</v>
+        <v>150171.62</v>
       </c>
       <c r="C5" s="11" t="n">
         <v>0</v>
@@ -4117,7 +4117,7 @@
         <v>0</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>351379.67</v>
+        <v>351243.08</v>
       </c>
     </row>
     <row r="6">
@@ -4165,7 +4165,7 @@
         </is>
       </c>
       <c r="B8" s="13" t="n">
-        <v>1462074.35</v>
+        <v>1462149.99</v>
       </c>
       <c r="C8" s="13" t="n">
         <v>2652712.4</v>
@@ -4174,7 +4174,7 @@
         <v>3295635.18</v>
       </c>
       <c r="E8" s="13" t="n">
-        <v>1852352.05</v>
+        <v>1852215.46</v>
       </c>
     </row>
     <row r="9">
@@ -4206,10 +4206,10 @@
         <v>0</v>
       </c>
       <c r="C10" s="13" t="n">
-        <v>842165.83</v>
+        <v>842219.7</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>963999.3</v>
+        <v>964090.51</v>
       </c>
       <c r="E10" s="15" t="n">
         <v>0</v>
@@ -4225,10 +4225,10 @@
         <v>398349.19</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>1645456.76</v>
+        <v>1645510.63</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>2290736.56</v>
+        <v>2290827.77</v>
       </c>
       <c r="E11" s="4" t="n">
         <v>814800.4300000001</v>
@@ -4241,16 +4241,16 @@
         </is>
       </c>
       <c r="B12" s="13" t="n">
-        <v>1063725.16</v>
+        <v>1063800.8</v>
       </c>
       <c r="C12" s="13" t="n">
-        <v>1007255.64</v>
+        <v>1007201.77</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>1004898.62</v>
+        <v>1004807.41</v>
       </c>
       <c r="E12" s="13" t="n">
-        <v>1037551.62</v>
+        <v>1037415.03</v>
       </c>
     </row>
     <row r="13">
@@ -4317,16 +4317,16 @@
         </is>
       </c>
       <c r="B16" s="13" t="n">
-        <v>802922.88</v>
+        <v>802998.52</v>
       </c>
       <c r="C16" s="13" t="n">
-        <v>479926.32</v>
+        <v>479872.45</v>
       </c>
       <c r="D16" s="13" t="n">
-        <v>351078.53</v>
+        <v>350987.32</v>
       </c>
       <c r="E16" s="13" t="n">
-        <v>740616.34</v>
+        <v>740479.75</v>
       </c>
     </row>
     <row r="17">
@@ -4345,7 +4345,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="19">
@@ -4392,10 +4392,10 @@
         <v>905662.2</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1007255.64</v>
+        <v>1007201.77</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>1004898.62</v>
+        <v>1004807.41</v>
       </c>
       <c r="E21" s="4" t="n">
         <v>669875.9399999999</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="C24" s="13" t="n">
-        <v>826100.01</v>
+        <v>826153.88</v>
       </c>
       <c r="D24" s="13" t="n">
-        <v>937464.5600000001</v>
+        <v>937555.77</v>
       </c>
       <c r="E24" s="15" t="n">
         <v>0</v>
@@ -4468,10 +4468,10 @@
         <v>905662.2</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>1007255.64</v>
+        <v>1007201.77</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>1004898.62</v>
+        <v>1004807.41</v>
       </c>
       <c r="E25" s="4" t="n">
         <v>669875.9399999999</v>
@@ -4598,7 +4598,7 @@
         </is>
       </c>
       <c r="B32" s="13" t="n">
-        <v>150095.98</v>
+        <v>150171.62</v>
       </c>
       <c r="C32" s="15" t="n">
         <v>0</v>
@@ -4607,7 +4607,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="13" t="n">
-        <v>351379.67</v>
+        <v>351243.08</v>
       </c>
     </row>
     <row r="33">
@@ -4617,16 +4617,16 @@
         </is>
       </c>
       <c r="B33" s="4" t="n">
-        <v>1063725.16</v>
+        <v>1063800.8</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>1007255.64</v>
+        <v>1007201.77</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>1004898.62</v>
+        <v>1004807.41</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>1037551.62</v>
+        <v>1037415.03</v>
       </c>
     </row>
     <row r="34">
@@ -4689,16 +4689,16 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>499890.57</v>
+        <v>498860.65</v>
       </c>
       <c r="C39" s="4" t="n">
-        <v>482682.92</v>
+        <v>481651.58</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>486204.76</v>
+        <v>485159.09</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>328575.45</v>
+        <v>327476.84</v>
       </c>
     </row>
     <row r="40">
@@ -4746,16 +4746,16 @@
         </is>
       </c>
       <c r="B42" s="13" t="n">
-        <v>640579.42</v>
+        <v>639549.5</v>
       </c>
       <c r="C42" s="13" t="n">
-        <v>657288.77</v>
+        <v>656257.4300000001</v>
       </c>
       <c r="D42" s="13" t="n">
-        <v>665370.1800000001</v>
+        <v>664324.51</v>
       </c>
       <c r="E42" s="13" t="n">
-        <v>903195.38</v>
+        <v>902096.77</v>
       </c>
     </row>
     <row r="43">
@@ -4822,16 +4822,16 @@
         </is>
       </c>
       <c r="B46" s="13" t="n">
-        <v>569544.12</v>
+        <v>568514.2</v>
       </c>
       <c r="C46" s="13" t="n">
-        <v>570328.12</v>
+        <v>569296.78</v>
       </c>
       <c r="D46" s="13" t="n">
-        <v>578256.1</v>
+        <v>577210.4300000001</v>
       </c>
       <c r="E46" s="13" t="n">
-        <v>607530.34</v>
+        <v>606431.73</v>
       </c>
     </row>
     <row r="47">
@@ -4844,13 +4844,13 @@
         <v>0.245</v>
       </c>
       <c r="C47" s="7" t="n">
-        <v>0.303</v>
+        <v>0.304</v>
       </c>
       <c r="D47" s="7" t="n">
         <v>0.307</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>0.9360000000000001</v>
+        <v>0.9379999999999999</v>
       </c>
     </row>
     <row r="48">
@@ -4898,16 +4898,16 @@
         </is>
       </c>
       <c r="B50" s="13" t="n">
-        <v>541690.49</v>
+        <v>540660.5699999999</v>
       </c>
       <c r="C50" s="13" t="n">
-        <v>535754.79</v>
+        <v>534723.45</v>
       </c>
       <c r="D50" s="13" t="n">
-        <v>542771.47</v>
+        <v>541725.8</v>
       </c>
       <c r="E50" s="13" t="n">
-        <v>493789.01</v>
+        <v>492690.4</v>
       </c>
     </row>
     <row r="51">
@@ -5179,16 +5179,16 @@
         </is>
       </c>
       <c r="B66" s="13" t="n">
-        <v>499890.57</v>
+        <v>498860.65</v>
       </c>
       <c r="C66" s="13" t="n">
-        <v>482682.92</v>
+        <v>481651.58</v>
       </c>
       <c r="D66" s="13" t="n">
-        <v>486204.76</v>
+        <v>485159.09</v>
       </c>
       <c r="E66" s="13" t="n">
-        <v>328575.45</v>
+        <v>327476.84</v>
       </c>
     </row>
     <row r="67">
@@ -5198,16 +5198,16 @@
         </is>
       </c>
       <c r="B67" s="4" t="n">
-        <v>569544.12</v>
+        <v>568514.2</v>
       </c>
       <c r="C67" s="4" t="n">
-        <v>570328.12</v>
+        <v>569296.78</v>
       </c>
       <c r="D67" s="4" t="n">
-        <v>578256.1</v>
+        <v>577210.4300000001</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>607530.34</v>
+        <v>606431.73</v>
       </c>
     </row>
     <row r="68">
@@ -5279,7 +5279,7 @@
         <v>0</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>22804.22</v>
+        <v>23766.23</v>
       </c>
     </row>
     <row r="74">
@@ -5336,7 +5336,7 @@
         <v>3116469.76</v>
       </c>
       <c r="E76" s="13" t="n">
-        <v>949156.67</v>
+        <v>950118.6800000001</v>
       </c>
     </row>
     <row r="77">
@@ -5365,13 +5365,13 @@
         </is>
       </c>
       <c r="B78" s="13" t="n">
-        <v>349794.59</v>
+        <v>348689.04</v>
       </c>
       <c r="C78" s="13" t="n">
-        <v>1324848.74</v>
+        <v>1323871.28</v>
       </c>
       <c r="D78" s="13" t="n">
-        <v>1450204.06</v>
+        <v>1449249.6</v>
       </c>
       <c r="E78" s="15" t="n">
         <v>0</v>
@@ -5384,13 +5384,13 @@
         </is>
       </c>
       <c r="B79" s="4" t="n">
-        <v>677108.48</v>
+        <v>676002.9300000001</v>
       </c>
       <c r="C79" s="4" t="n">
-        <v>2041179.02</v>
+        <v>2040201.56</v>
       </c>
       <c r="D79" s="4" t="n">
-        <v>2689827.24</v>
+        <v>2688872.78</v>
       </c>
       <c r="E79" s="4" t="n">
         <v>519135.39</v>
@@ -5403,16 +5403,16 @@
         </is>
       </c>
       <c r="B80" s="13" t="n">
-        <v>494181.05</v>
+        <v>495286.6</v>
       </c>
       <c r="C80" s="13" t="n">
-        <v>436927.53</v>
+        <v>437904.99</v>
       </c>
       <c r="D80" s="13" t="n">
-        <v>426642.52</v>
+        <v>427596.98</v>
       </c>
       <c r="E80" s="13" t="n">
-        <v>430021.28</v>
+        <v>430983.29</v>
       </c>
     </row>
     <row r="81">
@@ -5422,16 +5422,16 @@
         </is>
       </c>
       <c r="B81" s="7" t="n">
-        <v>2.357</v>
+        <v>2.352</v>
       </c>
       <c r="C81" s="7" t="n">
-        <v>5.639</v>
+        <v>5.626</v>
       </c>
       <c r="D81" s="7" t="n">
-        <v>7.247</v>
+        <v>7.23</v>
       </c>
       <c r="E81" s="7" t="n">
-        <v>2.13</v>
+        <v>2.125</v>
       </c>
     </row>
     <row r="82">
@@ -5441,13 +5441,13 @@
         </is>
       </c>
       <c r="B82" s="17" t="n">
-        <v>1.032</v>
+        <v>1.03</v>
       </c>
       <c r="C82" s="17" t="n">
-        <v>2.36</v>
+        <v>2.355</v>
       </c>
       <c r="D82" s="17" t="n">
-        <v>1.435</v>
+        <v>1.432</v>
       </c>
       <c r="E82" s="17" t="n">
         <v>-0.284</v>
@@ -5479,16 +5479,16 @@
         </is>
       </c>
       <c r="B84" s="13" t="n">
-        <v>261232.4</v>
+        <v>262337.95</v>
       </c>
       <c r="C84" s="18" t="n">
-        <v>-55828.46</v>
+        <v>-54851</v>
       </c>
       <c r="D84" s="18" t="n">
-        <v>-191692.94</v>
+        <v>-190738.48</v>
       </c>
       <c r="E84" s="13" t="n">
-        <v>246827.33</v>
+        <v>247789.34</v>
       </c>
     </row>
     <row r="85">
@@ -5504,10 +5504,10 @@
         <v>0</v>
       </c>
       <c r="D85" s="7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E85" s="7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -5551,13 +5551,13 @@
         </is>
       </c>
       <c r="B89" s="4" t="n">
-        <v>494181.05</v>
+        <v>495286.6</v>
       </c>
       <c r="C89" s="4" t="n">
-        <v>436927.53</v>
+        <v>437904.99</v>
       </c>
       <c r="D89" s="4" t="n">
-        <v>426642.52</v>
+        <v>427596.98</v>
       </c>
       <c r="E89" s="4" t="n">
         <v>396834.35</v>
@@ -5608,13 +5608,13 @@
         </is>
       </c>
       <c r="B92" s="13" t="n">
-        <v>343248.31</v>
+        <v>342142.76</v>
       </c>
       <c r="C92" s="13" t="n">
-        <v>1310522.13</v>
+        <v>1309544.67</v>
       </c>
       <c r="D92" s="13" t="n">
-        <v>1425411.6</v>
+        <v>1424457.14</v>
       </c>
       <c r="E92" s="15" t="n">
         <v>0</v>
@@ -5627,13 +5627,13 @@
         </is>
       </c>
       <c r="B93" s="4" t="n">
-        <v>494181.05</v>
+        <v>495286.6</v>
       </c>
       <c r="C93" s="4" t="n">
-        <v>436927.53</v>
+        <v>437904.99</v>
       </c>
       <c r="D93" s="4" t="n">
-        <v>426642.52</v>
+        <v>427596.98</v>
       </c>
       <c r="E93" s="4" t="n">
         <v>396834.35</v>
@@ -5769,7 +5769,7 @@
         <v>0</v>
       </c>
       <c r="E100" s="13" t="n">
-        <v>22804.22</v>
+        <v>23766.23</v>
       </c>
     </row>
     <row r="101">
@@ -5779,16 +5779,16 @@
         </is>
       </c>
       <c r="B101" s="4" t="n">
-        <v>494181.05</v>
+        <v>495286.6</v>
       </c>
       <c r="C101" s="4" t="n">
-        <v>436927.53</v>
+        <v>437904.99</v>
       </c>
       <c r="D101" s="4" t="n">
-        <v>426642.52</v>
+        <v>427596.98</v>
       </c>
       <c r="E101" s="4" t="n">
-        <v>430021.28</v>
+        <v>430983.29</v>
       </c>
     </row>
     <row r="102">
@@ -5882,16 +5882,16 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>56469.52</v>
+        <v>56599.03</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>58826.54</v>
+        <v>58993.39</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>26173.54</v>
+        <v>26385.77</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>142226.37</v>
+        <v>142302.01</v>
       </c>
     </row>
     <row r="6">
@@ -5964,16 +5964,16 @@
         </is>
       </c>
       <c r="B11" s="19" t="n">
-        <v>-784</v>
+        <v>-782.58</v>
       </c>
       <c r="C11" s="19" t="n">
-        <v>-8711.98</v>
+        <v>-8696.23</v>
       </c>
       <c r="D11" s="19" t="n">
-        <v>-37986.22</v>
+        <v>-37917.53</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>60212.18</v>
+        <v>59182.26</v>
       </c>
     </row>
     <row r="12">
@@ -6046,16 +6046,16 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>57253.52</v>
+        <v>57381.61</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>67538.53</v>
+        <v>67689.62</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>64159.77</v>
+        <v>64303.31</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>82014.2</v>
+        <v>83119.75</v>
       </c>
     </row>
     <row r="18">
@@ -6065,16 +6065,16 @@
         </is>
       </c>
       <c r="B18" s="15" t="n">
-        <v>47.92</v>
+        <v>47.77</v>
       </c>
       <c r="C18" s="13" t="n">
-        <v>239.59</v>
+        <v>238.83</v>
       </c>
       <c r="D18" s="13" t="n">
-        <v>1006.26</v>
+        <v>1003.08</v>
       </c>
       <c r="E18" s="13" t="n">
-        <v>7187.56</v>
+        <v>7164.84</v>
       </c>
     </row>
     <row r="19">
@@ -6166,13 +6166,13 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>1007255.64</v>
+        <v>1007201.77</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>1004898.62</v>
+        <v>1004807.41</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>1037551.62</v>
+        <v>1037415.03</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>921498.79</v>
@@ -6185,16 +6185,16 @@
         </is>
       </c>
       <c r="B6" s="13" t="n">
-        <v>56469.52</v>
+        <v>56599.03</v>
       </c>
       <c r="C6" s="13" t="n">
-        <v>58826.54</v>
+        <v>58993.39</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>26173.54</v>
+        <v>26385.77</v>
       </c>
       <c r="E6" s="13" t="n">
-        <v>142226.37</v>
+        <v>142302.01</v>
       </c>
     </row>
     <row r="7">
@@ -6242,16 +6242,16 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>1063725.16</v>
+        <v>1063800.8</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>1063725.16</v>
+        <v>1063800.8</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>1063725.16</v>
+        <v>1063800.8</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>1063725.16</v>
+        <v>1063800.8</v>
       </c>
     </row>
     <row r="10">
@@ -6261,16 +6261,16 @@
         </is>
       </c>
       <c r="B10" s="20" t="n">
-        <v>5.61</v>
+        <v>5.62</v>
       </c>
       <c r="C10" s="20" t="n">
-        <v>5.85</v>
+        <v>5.87</v>
       </c>
       <c r="D10" s="20" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="E10" s="20" t="n">
-        <v>15.43</v>
+        <v>15.44</v>
       </c>
     </row>
     <row r="11">
@@ -6283,10 +6283,10 @@
         <v>0</v>
       </c>
       <c r="C11" s="22" t="n">
-        <v>-9.4</v>
+        <v>-9.41</v>
       </c>
       <c r="D11" s="22" t="n">
-        <v>-9.4</v>
+        <v>-9.41</v>
       </c>
       <c r="E11" s="22" t="n">
         <v>-9.470000000000001</v>
@@ -6333,13 +6333,13 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>570328.12</v>
+        <v>569296.78</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>578256.1</v>
+        <v>577210.4300000001</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>607530.34</v>
+        <v>606431.73</v>
       </c>
       <c r="E15" s="4" t="n">
         <v>509331.94</v>
@@ -6352,16 +6352,16 @@
         </is>
       </c>
       <c r="B16" s="18" t="n">
-        <v>-784</v>
+        <v>-782.58</v>
       </c>
       <c r="C16" s="18" t="n">
-        <v>-8711.98</v>
+        <v>-8696.23</v>
       </c>
       <c r="D16" s="18" t="n">
-        <v>-37986.22</v>
+        <v>-37917.53</v>
       </c>
       <c r="E16" s="13" t="n">
-        <v>60212.18</v>
+        <v>59182.26</v>
       </c>
     </row>
     <row r="17">
@@ -6409,16 +6409,16 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>569544.12</v>
+        <v>568514.2</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>569544.12</v>
+        <v>568514.2</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>569544.12</v>
+        <v>568514.2</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>569544.12</v>
+        <v>568514.2</v>
       </c>
     </row>
     <row r="20">
@@ -6437,7 +6437,7 @@
         <v>-6.25</v>
       </c>
       <c r="E20" s="20" t="n">
-        <v>11.82</v>
+        <v>11.62</v>
       </c>
     </row>
     <row r="21">
@@ -6500,13 +6500,13 @@
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>436927.53</v>
+        <v>437904.99</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>426642.52</v>
+        <v>427596.98</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>430021.28</v>
+        <v>430983.29</v>
       </c>
       <c r="E25" s="4" t="n">
         <v>412166.85</v>
@@ -6519,16 +6519,16 @@
         </is>
       </c>
       <c r="B26" s="13" t="n">
-        <v>57253.52</v>
+        <v>57381.61</v>
       </c>
       <c r="C26" s="13" t="n">
-        <v>67538.53</v>
+        <v>67689.62</v>
       </c>
       <c r="D26" s="13" t="n">
-        <v>64159.77</v>
+        <v>64303.31</v>
       </c>
       <c r="E26" s="13" t="n">
-        <v>82014.2</v>
+        <v>83119.75</v>
       </c>
     </row>
     <row r="27">
@@ -6576,16 +6576,16 @@
         </is>
       </c>
       <c r="B29" s="4" t="n">
-        <v>494181.05</v>
+        <v>495286.6</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>494181.05</v>
+        <v>495286.6</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>494181.05</v>
+        <v>495286.6</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>494181.05</v>
+        <v>495286.6</v>
       </c>
     </row>
     <row r="30">
@@ -6604,7 +6604,7 @@
         <v>14.92</v>
       </c>
       <c r="E30" s="20" t="n">
-        <v>19.9</v>
+        <v>20.17</v>
       </c>
     </row>
     <row r="31">
@@ -6673,7 +6673,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>58826.54</v>
+        <v>58993.39</v>
       </c>
     </row>
     <row r="5">
@@ -6693,7 +6693,7 @@
         </is>
       </c>
       <c r="B6" s="19" t="n">
-        <v>-963999.3</v>
+        <v>-964090.51</v>
       </c>
     </row>
     <row r="7">
@@ -6703,7 +6703,7 @@
         </is>
       </c>
       <c r="B7" s="19" t="n">
-        <v>-796859.85</v>
+        <v>-796784.21</v>
       </c>
     </row>
     <row r="8">
@@ -6723,7 +6723,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>150095.98</v>
+        <v>150171.62</v>
       </c>
     </row>
     <row r="11">
@@ -7700,7 +7700,7 @@
         </is>
       </c>
       <c r="B96" s="4" t="n">
-        <v>1011218.51</v>
+        <v>1011202.12</v>
       </c>
     </row>
     <row r="97">
@@ -7710,7 +7710,7 @@
         </is>
       </c>
       <c r="B97" s="13" t="n">
-        <v>1025407</v>
+        <v>1025356.19</v>
       </c>
     </row>
     <row r="98">
@@ -7720,7 +7720,7 @@
         </is>
       </c>
       <c r="B98" s="4" t="n">
-        <v>1026941.31</v>
+        <v>1026905.51</v>
       </c>
     </row>
     <row r="99">
@@ -7730,7 +7730,7 @@
         </is>
       </c>
       <c r="B99" s="13" t="n">
-        <v>1015258.85</v>
+        <v>1015273.3</v>
       </c>
     </row>
     <row r="100">
@@ -7740,7 +7740,7 @@
         </is>
       </c>
       <c r="B100" s="4" t="n">
-        <v>1003003.03</v>
+        <v>1003025.8</v>
       </c>
     </row>
     <row r="101">
@@ -7750,7 +7750,7 @@
         </is>
       </c>
       <c r="B101" s="13" t="n">
-        <v>1013068.4</v>
+        <v>1013098.34</v>
       </c>
     </row>
     <row r="102">
@@ -7760,7 +7760,7 @@
         </is>
       </c>
       <c r="B102" s="4" t="n">
-        <v>1026667.89</v>
+        <v>1026718.34</v>
       </c>
     </row>
     <row r="103">
@@ -7770,7 +7770,7 @@
         </is>
       </c>
       <c r="B103" s="13" t="n">
-        <v>1053397.75</v>
+        <v>1053504.94</v>
       </c>
     </row>
     <row r="104">
@@ -7780,7 +7780,7 @@
         </is>
       </c>
       <c r="B104" s="4" t="n">
-        <v>1050736.08</v>
+        <v>1050844.96</v>
       </c>
     </row>
     <row r="105">
@@ -7790,7 +7790,7 @@
         </is>
       </c>
       <c r="B105" s="13" t="n">
-        <v>1049499.07</v>
+        <v>1049581.91</v>
       </c>
     </row>
     <row r="106">
@@ -7800,7 +7800,7 @@
         </is>
       </c>
       <c r="B106" s="4" t="n">
-        <v>1049134.93</v>
+        <v>1049200.21</v>
       </c>
     </row>
     <row r="107">
@@ -7810,7 +7810,7 @@
         </is>
       </c>
       <c r="B107" s="13" t="n">
-        <v>1042919.9</v>
+        <v>1042965.78</v>
       </c>
     </row>
     <row r="108">
@@ -7820,7 +7820,7 @@
         </is>
       </c>
       <c r="B108" s="4" t="n">
-        <v>1048685.92</v>
+        <v>1048734.43</v>
       </c>
     </row>
     <row r="109">
@@ -7830,7 +7830,7 @@
         </is>
       </c>
       <c r="B109" s="13" t="n">
-        <v>1042773.4</v>
+        <v>1042822.5</v>
       </c>
     </row>
     <row r="110">
@@ -7840,7 +7840,7 @@
         </is>
       </c>
       <c r="B110" s="4" t="n">
-        <v>1044235.83</v>
+        <v>1044292.9</v>
       </c>
     </row>
     <row r="111">
@@ -7850,7 +7850,7 @@
         </is>
       </c>
       <c r="B111" s="13" t="n">
-        <v>1070354.14</v>
+        <v>1070408.83</v>
       </c>
     </row>
     <row r="112">
@@ -7860,7 +7860,7 @@
         </is>
       </c>
       <c r="B112" s="4" t="n">
-        <v>1061514.84</v>
+        <v>1061559.43</v>
       </c>
     </row>
     <row r="113">
@@ -7870,7 +7870,7 @@
         </is>
       </c>
       <c r="B113" s="13" t="n">
-        <v>1074870.62</v>
+        <v>1074879.59</v>
       </c>
     </row>
     <row r="114">
@@ -7880,7 +7880,7 @@
         </is>
       </c>
       <c r="B114" s="4" t="n">
-        <v>1080512.52</v>
+        <v>1080503.54</v>
       </c>
     </row>
     <row r="115">
@@ -7890,7 +7890,7 @@
         </is>
       </c>
       <c r="B115" s="13" t="n">
-        <v>1086924.48</v>
+        <v>1086894.67</v>
       </c>
     </row>
     <row r="116">
@@ -7900,7 +7900,7 @@
         </is>
       </c>
       <c r="B116" s="4" t="n">
-        <v>1071780.32</v>
+        <v>1071796.37</v>
       </c>
     </row>
     <row r="117">
@@ -7910,7 +7910,7 @@
         </is>
       </c>
       <c r="B117" s="13" t="n">
-        <v>1065526.09</v>
+        <v>1065522.69</v>
       </c>
     </row>
     <row r="118">
@@ -7920,7 +7920,7 @@
         </is>
       </c>
       <c r="B118" s="4" t="n">
-        <v>1080594.32</v>
+        <v>1080563.67</v>
       </c>
     </row>
     <row r="119">
@@ -7930,7 +7930,7 @@
         </is>
       </c>
       <c r="B119" s="13" t="n">
-        <v>1075591.99</v>
+        <v>1075540.76</v>
       </c>
     </row>
     <row r="120">
@@ -7940,7 +7940,7 @@
         </is>
       </c>
       <c r="B120" s="4" t="n">
-        <v>1071013.67</v>
+        <v>1070952.2</v>
       </c>
     </row>
     <row r="121">
@@ -7950,7 +7950,7 @@
         </is>
       </c>
       <c r="B121" s="13" t="n">
-        <v>1073689.47</v>
+        <v>1073612.17</v>
       </c>
     </row>
     <row r="122">
@@ -7960,7 +7960,7 @@
         </is>
       </c>
       <c r="B122" s="4" t="n">
-        <v>1074236.64</v>
+        <v>1074160.56</v>
       </c>
     </row>
     <row r="123">
@@ -7970,7 +7970,7 @@
         </is>
       </c>
       <c r="B123" s="13" t="n">
-        <v>1084547.15</v>
+        <v>1084460.75</v>
       </c>
     </row>
     <row r="124">
@@ -7980,7 +7980,7 @@
         </is>
       </c>
       <c r="B124" s="4" t="n">
-        <v>1085528.37</v>
+        <v>1085444.17</v>
       </c>
     </row>
     <row r="125">
@@ -7990,7 +7990,7 @@
         </is>
       </c>
       <c r="B125" s="13" t="n">
-        <v>1092616.33</v>
+        <v>1092531.84</v>
       </c>
     </row>
     <row r="126">
@@ -8000,7 +8000,7 @@
         </is>
       </c>
       <c r="B126" s="4" t="n">
-        <v>1092781.06</v>
+        <v>1092690.79</v>
       </c>
     </row>
     <row r="127">
@@ -8010,7 +8010,7 @@
         </is>
       </c>
       <c r="B127" s="13" t="n">
-        <v>1053336.82</v>
+        <v>1053158.31</v>
       </c>
     </row>
     <row r="128">
@@ -8020,7 +8020,7 @@
         </is>
       </c>
       <c r="B128" s="4" t="n">
-        <v>1049687.33</v>
+        <v>1049512.64</v>
       </c>
     </row>
     <row r="129">
@@ -8030,7 +8030,7 @@
         </is>
       </c>
       <c r="B129" s="13" t="n">
-        <v>1044100.12</v>
+        <v>1043936.06</v>
       </c>
     </row>
     <row r="130">
@@ -8040,7 +8040,7 @@
         </is>
       </c>
       <c r="B130" s="4" t="n">
-        <v>1032626.83</v>
+        <v>1032472.74</v>
       </c>
     </row>
     <row r="131">
@@ -8050,7 +8050,7 @@
         </is>
       </c>
       <c r="B131" s="13" t="n">
-        <v>1039700.39</v>
+        <v>1039556.14</v>
       </c>
     </row>
     <row r="132">
@@ -8060,7 +8060,7 @@
         </is>
       </c>
       <c r="B132" s="4" t="n">
-        <v>1037551.62</v>
+        <v>1037415.03</v>
       </c>
     </row>
     <row r="133">
@@ -8070,7 +8070,7 @@
         </is>
       </c>
       <c r="B133" s="13" t="n">
-        <v>1019311.74</v>
+        <v>1019194.66</v>
       </c>
     </row>
     <row r="134">
@@ -8080,7 +8080,7 @@
         </is>
       </c>
       <c r="B134" s="4" t="n">
-        <v>1014163.76</v>
+        <v>1014068.88</v>
       </c>
     </row>
     <row r="135">
@@ -8090,7 +8090,7 @@
         </is>
       </c>
       <c r="B135" s="13" t="n">
-        <v>999293.04</v>
+        <v>999221.6800000001</v>
       </c>
     </row>
     <row r="136">
@@ -8100,7 +8100,7 @@
         </is>
       </c>
       <c r="B136" s="4" t="n">
-        <v>1011409.78</v>
+        <v>1011311.18</v>
       </c>
     </row>
     <row r="137">
@@ -8110,7 +8110,7 @@
         </is>
       </c>
       <c r="B137" s="13" t="n">
-        <v>1014540.8</v>
+        <v>1014433.88</v>
       </c>
     </row>
     <row r="138">
@@ -8120,7 +8120,7 @@
         </is>
       </c>
       <c r="B138" s="4" t="n">
-        <v>1011881.11</v>
+        <v>1011774.92</v>
       </c>
     </row>
     <row r="139">
@@ -8130,7 +8130,7 @@
         </is>
       </c>
       <c r="B139" s="13" t="n">
-        <v>998415.39</v>
+        <v>998320.26</v>
       </c>
     </row>
     <row r="140">
@@ -8140,7 +8140,7 @@
         </is>
       </c>
       <c r="B140" s="4" t="n">
-        <v>1014351.76</v>
+        <v>1014291.81</v>
       </c>
     </row>
     <row r="141">
@@ -8150,7 +8150,7 @@
         </is>
       </c>
       <c r="B141" s="13" t="n">
-        <v>1023498.77</v>
+        <v>1023430.49</v>
       </c>
     </row>
     <row r="142">
@@ -8160,7 +8160,7 @@
         </is>
       </c>
       <c r="B142" s="4" t="n">
-        <v>1023696.66</v>
+        <v>1023647.26</v>
       </c>
     </row>
     <row r="143">
@@ -8170,7 +8170,7 @@
         </is>
       </c>
       <c r="B143" s="13" t="n">
-        <v>996887.45</v>
+        <v>996791.04</v>
       </c>
     </row>
     <row r="144">
@@ -8180,7 +8180,7 @@
         </is>
       </c>
       <c r="B144" s="4" t="n">
-        <v>1016573.57</v>
+        <v>1016545.25</v>
       </c>
     </row>
     <row r="145">
@@ -8190,7 +8190,7 @@
         </is>
       </c>
       <c r="B145" s="13" t="n">
-        <v>997861.24</v>
+        <v>997800.67</v>
       </c>
     </row>
     <row r="146">
@@ -8200,7 +8200,7 @@
         </is>
       </c>
       <c r="B146" s="4" t="n">
-        <v>991493.7</v>
+        <v>991400.37</v>
       </c>
     </row>
     <row r="147">
@@ -8210,7 +8210,7 @@
         </is>
       </c>
       <c r="B147" s="13" t="n">
-        <v>989347.35</v>
+        <v>989233.28</v>
       </c>
     </row>
     <row r="148">
@@ -8220,7 +8220,7 @@
         </is>
       </c>
       <c r="B148" s="4" t="n">
-        <v>1004898.62</v>
+        <v>1004807.41</v>
       </c>
     </row>
     <row r="149">
@@ -8230,7 +8230,7 @@
         </is>
       </c>
       <c r="B149" s="13" t="n">
-        <v>1099657.36</v>
+        <v>1099781.06</v>
       </c>
     </row>
     <row r="150">
@@ -8240,7 +8240,7 @@
         </is>
       </c>
       <c r="B150" s="4" t="n">
-        <v>1108417.28</v>
+        <v>1108558.05</v>
       </c>
     </row>
     <row r="151">
@@ -8250,7 +8250,7 @@
         </is>
       </c>
       <c r="B151" s="13" t="n">
-        <v>1111711.73</v>
+        <v>1111869.67</v>
       </c>
     </row>
     <row r="152">
@@ -8260,7 +8260,7 @@
         </is>
       </c>
       <c r="B152" s="4" t="n">
-        <v>1007255.64</v>
+        <v>1007201.77</v>
       </c>
     </row>
     <row r="153">
@@ -8270,7 +8270,7 @@
         </is>
       </c>
       <c r="B153" s="13" t="n">
-        <v>1063725.16</v>
+        <v>1063800.8</v>
       </c>
     </row>
   </sheetData>
@@ -8375,7 +8375,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>1063725.16</v>
+        <v>1063800.8</v>
       </c>
       <c r="C4" s="4" t="n">
         <v>905662.2</v>
@@ -8396,7 +8396,7 @@
         <v>0.477</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>122.59</v>
+        <v>122.58</v>
       </c>
       <c r="J4" s="5" t="n">
         <v>61.29</v>
@@ -8412,7 +8412,7 @@
         </is>
       </c>
       <c r="B5" s="13" t="n">
-        <v>569544.12</v>
+        <v>568514.2</v>
       </c>
       <c r="C5" s="13" t="n">
         <v>68232.84</v>
@@ -8433,10 +8433,10 @@
         <v>-0.005</v>
       </c>
       <c r="I5" s="25" t="n">
-        <v>24.45</v>
+        <v>24.5</v>
       </c>
       <c r="J5" s="25" t="n">
-        <v>12.23</v>
+        <v>12.25</v>
       </c>
       <c r="K5" s="26" t="n">
         <v>1</v>
@@ -8449,7 +8449,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>494181.05</v>
+        <v>495286.6</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>837429.36</v>
@@ -8464,16 +8464,16 @@
         <v>510115.47</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>2.357</v>
+        <v>2.352</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>1.032</v>
+        <v>1.03</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>235.69</v>
+        <v>235.17</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>117.85</v>
+        <v>117.58</v>
       </c>
       <c r="K6" s="24" t="n">
         <v>7</v>
@@ -8563,7 +8563,7 @@
         <v>237273.6</v>
       </c>
       <c r="D6" s="21" t="n">
-        <v>22.31</v>
+        <v>22.3</v>
       </c>
       <c r="E6" s="21" t="n">
         <v>18.2</v>
@@ -8954,7 +8954,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>47.96</v>
+        <v>47.95</v>
       </c>
     </row>
     <row r="6">

--- a/trading_signals/risk_management/risk_workbook_20260609_031841.xlsx
+++ b/trading_signals/risk_management/risk_workbook_20260609_031841.xlsx
@@ -728,7 +728,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Signal date 2026-06-08  ·  Generated 2026-06-24T18:50:42  ·  Scope: MRPT+MTFS pairs book (model-based, broker-reconciled)</t>
+          <t>Signal date 2026-06-08  ·  Generated 2026-06-25T01:17:59  ·  Scope: MRPT+MTFS pairs book (model-based, broker-reconciled)</t>
         </is>
       </c>
     </row>

--- a/trading_signals/risk_management/risk_workbook_20260609_031841.xlsx
+++ b/trading_signals/risk_management/risk_workbook_20260609_031841.xlsx
@@ -728,7 +728,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Signal date 2026-06-08  ·  Generated 2026-06-25T01:17:59  ·  Scope: MRPT+MTFS pairs book (model-based, broker-reconciled)</t>
+          <t>Signal date 2026-06-08  ·  Generated 2026-06-25T01:35:51  ·  Scope: MRPT+MTFS pairs book (model-based, broker-reconciled)</t>
         </is>
       </c>
     </row>

--- a/trading_signals/risk_management/risk_workbook_20260609_031841.xlsx
+++ b/trading_signals/risk_management/risk_workbook_20260609_031841.xlsx
@@ -728,7 +728,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Signal date 2026-06-08  ·  Generated 2026-06-25T01:35:51  ·  Scope: MRPT+MTFS pairs book (model-based, broker-reconciled)</t>
+          <t>Signal date 2026-06-08  ·  Generated 2026-06-25T01:49:15  ·  Scope: MRPT+MTFS pairs book (model-based, broker-reconciled)</t>
         </is>
       </c>
     </row>
